--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487786_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487786_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.4796</v>
+        <v>5.4678</v>
       </c>
       <c r="E2" t="n">
-        <v>2.4831</v>
+        <v>3.5594</v>
       </c>
       <c r="F2" t="n">
-        <v>1.9965</v>
+        <v>1.9084</v>
       </c>
       <c r="G2" t="n">
         <v>0.865</v>
@@ -610,13 +610,13 @@
         <v>2.4974</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.6956</v>
+        <v>-0.7074</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.109</v>
+        <v>0.9673</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.5866</v>
+        <v>-1.6747</v>
       </c>
       <c r="V2" t="n">
         <v>2.8127</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.8262</v>
+        <v>4.0633</v>
       </c>
       <c r="E3" t="n">
-        <v>4.2239</v>
+        <v>5.0206</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.3977</v>
+        <v>-0.9573</v>
       </c>
       <c r="G3" t="n">
         <v>3.4951</v>
@@ -688,13 +688,13 @@
         <v>2.0812</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.8157</v>
+        <v>-0.5785</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3824</v>
+        <v>0.4144</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.4333</v>
+        <v>-0.9929</v>
       </c>
       <c r="V3" t="n">
         <v>0.1061</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. LACUNZA ABECIA</t>
+          <t>J. DJERY</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.518</v>
+        <v>1.2271</v>
       </c>
       <c r="E4" t="n">
-        <v>2.8827</v>
+        <v>-0.1644</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3647</v>
+        <v>1.3915</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.4229</v>
+        <v>0.6788999999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0915</v>
+        <v>1.2325</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.5145</v>
+        <v>-0.5535</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.4062</v>
+        <v>0.2587</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8266</v>
+        <v>0.1019</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.2328</v>
+        <v>0.1568</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.0168</v>
+        <v>0.4203</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.7351</v>
+        <v>1.1306</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2817</v>
+        <v>-0.7103</v>
       </c>
       <c r="P4" t="n">
-        <v>1.8731</v>
+        <v>-0.8325</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-2.0812</v>
       </c>
       <c r="R4" t="n">
-        <v>1.8731</v>
+        <v>1.2487</v>
       </c>
       <c r="S4" t="n">
-        <v>2.4217</v>
+        <v>-0.4945</v>
       </c>
       <c r="T4" t="n">
-        <v>2.4751</v>
+        <v>0.4906</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0534</v>
+        <v>-0.9851</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.3538</v>
+        <v>1.8751</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8137</v>
+        <v>1.1675</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.1675</v>
+        <v>0.7076</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. DJERY</t>
+          <t>J. LACUNZA ABECIA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2005</v>
+        <v>1.0351</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1337</v>
+        <v>1.4292</v>
       </c>
       <c r="F5" t="n">
-        <v>2.0668</v>
+        <v>-0.394</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6788999999999999</v>
+        <v>-1.4229</v>
       </c>
       <c r="H5" t="n">
-        <v>1.2325</v>
+        <v>0.0915</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5535</v>
+        <v>-1.5145</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2587</v>
+        <v>-0.4062</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1019</v>
+        <v>0.8266</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1568</v>
+        <v>-1.2328</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4203</v>
+        <v>-1.0168</v>
       </c>
       <c r="N5" t="n">
-        <v>1.1306</v>
+        <v>-0.7351</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.7103</v>
+        <v>-0.2817</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.8325</v>
+        <v>1.8731</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.0812</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.2487</v>
+        <v>1.8731</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4789</v>
+        <v>0.9388</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7887</v>
+        <v>1.0216</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3098</v>
+        <v>-0.0828</v>
       </c>
       <c r="V5" t="n">
-        <v>1.8751</v>
+        <v>-0.3538</v>
       </c>
       <c r="W5" t="n">
-        <v>1.1675</v>
+        <v>0.8137</v>
       </c>
       <c r="X5" t="n">
-        <v>0.7076</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N. DEL VAL GARCIA</t>
+          <t>J. POTIER</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1021</v>
+        <v>0.9886</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.361</v>
+        <v>1.3892</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2589</v>
+        <v>-0.4005</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.823</v>
+        <v>3.0179</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6335</v>
+        <v>1.1728</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.4565</v>
+        <v>1.8451</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.0596</v>
+        <v>3.0917</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1151</v>
+        <v>0.7159</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.1747</v>
+        <v>2.3758</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.7634</v>
+        <v>-0.0738</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5183</v>
+        <v>0.4569</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.2818</v>
+        <v>-0.5306999999999999</v>
       </c>
       <c r="P6" t="n">
-        <v>1.0406</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-2.0812</v>
       </c>
       <c r="R6" t="n">
-        <v>1.0406</v>
+        <v>2.0812</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3197</v>
+        <v>-1.5694</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3014</v>
+        <v>0.3787</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0183</v>
+        <v>-1.948</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.4599</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.4599</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. POTIER</t>
+          <t>N. DEL VAL GARCIA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5429</v>
+        <v>0.341</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1219</v>
+        <v>-0.1234</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.6647999999999999</v>
+        <v>0.4644</v>
       </c>
       <c r="G7" t="n">
-        <v>3.0179</v>
+        <v>-0.823</v>
       </c>
       <c r="H7" t="n">
-        <v>1.1728</v>
+        <v>0.6335</v>
       </c>
       <c r="I7" t="n">
-        <v>1.8451</v>
+        <v>-1.4565</v>
       </c>
       <c r="J7" t="n">
-        <v>3.0917</v>
+        <v>-0.0596</v>
       </c>
       <c r="K7" t="n">
-        <v>0.7159</v>
+        <v>0.1151</v>
       </c>
       <c r="L7" t="n">
-        <v>2.3758</v>
+        <v>-0.1747</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.0738</v>
+        <v>-0.7634</v>
       </c>
       <c r="N7" t="n">
-        <v>0.4569</v>
+        <v>0.5183</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.5306999999999999</v>
+        <v>-1.2818</v>
       </c>
       <c r="P7" t="n">
+        <v>1.0406</v>
+      </c>
+      <c r="Q7" t="n">
         <v>0</v>
       </c>
-      <c r="Q7" t="n">
-        <v>-2.0812</v>
-      </c>
       <c r="R7" t="n">
-        <v>2.0812</v>
+        <v>1.0406</v>
       </c>
       <c r="S7" t="n">
-        <v>-3.1009</v>
+        <v>0.1235</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8885999999999999</v>
+        <v>-0.0638</v>
       </c>
       <c r="U7" t="n">
-        <v>-2.2122</v>
+        <v>0.1873</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.4599</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.4599</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5962</v>
+        <v>0.0999</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.4447</v>
+        <v>0.3101</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1515</v>
+        <v>-0.2102</v>
       </c>
       <c r="G8" t="n">
         <v>-3.4917</v>
@@ -1078,13 +1078,13 @@
         <v>1.6649</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.1045</v>
+        <v>-0.4084</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1743</v>
+        <v>0.5806</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.9303</v>
+        <v>-0.989</v>
       </c>
       <c r="V8" t="n">
         <v>2.3351</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. FERNANDEZ CHOCARRO</t>
+          <t>C. ZIZIC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.9476</v>
+        <v>-1.4145</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3802</v>
+        <v>-1.2853</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.5674</v>
+        <v>-0.1292</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.7655999999999999</v>
+        <v>2.1469</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.9933999999999999</v>
+        <v>2.32</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2278</v>
+        <v>-0.1731</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.1001</v>
+        <v>1.2244</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.2177</v>
+        <v>1.1853</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1176</v>
+        <v>0.0392</v>
       </c>
       <c r="M9" t="n">
-        <v>0.3345</v>
+        <v>0.9224</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2243</v>
+        <v>1.1347</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1102</v>
+        <v>-0.2123</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.4568</v>
+        <v>-2.7055</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.0812</v>
+        <v>-3.1218</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6244</v>
+        <v>0.4162</v>
       </c>
       <c r="S9" t="n">
-        <v>1.2748</v>
+        <v>0.8954</v>
       </c>
       <c r="T9" t="n">
-        <v>1.6336</v>
+        <v>0.9659</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3588</v>
+        <v>-0.0704</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-1.7513</v>
       </c>
       <c r="W9" t="n">
-        <v>1.1675</v>
+        <v>-0.3538</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.1675</v>
+        <v>-1.3975</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C. ZIZIC</t>
+          <t>P. FERNANDEZ CHOCARRO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.2491</v>
+        <v>-2.0779</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.2667</v>
+        <v>-1.4518</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0176</v>
+        <v>-0.6261</v>
       </c>
       <c r="G10" t="n">
-        <v>2.1469</v>
+        <v>-0.7655999999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>2.32</v>
+        <v>-0.9933999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1731</v>
+        <v>0.2278</v>
       </c>
       <c r="J10" t="n">
-        <v>1.2244</v>
+        <v>-1.1001</v>
       </c>
       <c r="K10" t="n">
-        <v>1.1853</v>
+        <v>-1.2177</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0392</v>
+        <v>0.1176</v>
       </c>
       <c r="M10" t="n">
-        <v>0.9224</v>
+        <v>0.3345</v>
       </c>
       <c r="N10" t="n">
-        <v>1.1347</v>
+        <v>0.2243</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2123</v>
+        <v>0.1102</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.7055</v>
+        <v>-1.4568</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.1218</v>
+        <v>-2.0812</v>
       </c>
       <c r="R10" t="n">
-        <v>0.4162</v>
+        <v>0.6244</v>
       </c>
       <c r="S10" t="n">
-        <v>1.0608</v>
+        <v>0.1445</v>
       </c>
       <c r="T10" t="n">
-        <v>0.9844000000000001</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0764</v>
+        <v>-0.4175</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.7513</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.3538</v>
+        <v>1.1675</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.3975</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-7.5224</v>
+        <v>-6.7093</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.0456</v>
+        <v>-1.3793</v>
       </c>
       <c r="F11" t="n">
-        <v>-5.4768</v>
+        <v>-5.33</v>
       </c>
       <c r="G11" t="n">
         <v>-1.0675</v>
@@ -1312,13 +1312,13 @@
         <v>1.0406</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.1386</v>
+        <v>-1.3255</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6277</v>
+        <v>0.0386</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.5109</v>
+        <v>-1.3641</v>
       </c>
       <c r="V11" t="n">
         <v>-4.3163</v>
@@ -1345,19 +1345,19 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>1.063999999999999</v>
+        <v>3.021100000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>5.347100000000001</v>
+        <v>7.304299999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.283099999999999</v>
+        <v>-4.283</v>
       </c>
       <c r="G12" t="n">
-        <v>2.6331</v>
+        <v>2.633100000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>7.6339</v>
+        <v>7.633899999999999</v>
       </c>
       <c r="I12" t="n">
         <v>-5.0007</v>
@@ -1369,7 +1369,7 @@
         <v>3.9828</v>
       </c>
       <c r="L12" t="n">
-        <v>0.6735999999999995</v>
+        <v>0.6735999999999998</v>
       </c>
       <c r="M12" t="n">
         <v>-2.0231</v>
@@ -1390,19 +1390,19 @@
         <v>14.5683</v>
       </c>
       <c r="S12" t="n">
-        <v>-4.938800000000001</v>
+        <v>-2.9815</v>
       </c>
       <c r="T12" t="n">
-        <v>3.3984</v>
+        <v>5.3559</v>
       </c>
       <c r="U12" t="n">
-        <v>-8.337199999999999</v>
+        <v>-8.337200000000001</v>
       </c>
       <c r="V12" t="n">
         <v>0.2477</v>
       </c>
       <c r="W12" t="n">
-        <v>8.738800000000001</v>
+        <v>8.738799999999999</v>
       </c>
       <c r="X12" t="n">
         <v>-8.491</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>11.1508</v>
+        <v>10.065</v>
       </c>
       <c r="E13" t="n">
-        <v>9.3018</v>
+        <v>8.337400000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>1.849</v>
+        <v>1.7276</v>
       </c>
       <c r="G13" t="n">
         <v>5.0914</v>
@@ -1468,13 +1468,13 @@
         <v>1.4568</v>
       </c>
       <c r="S13" t="n">
-        <v>2.4517</v>
+        <v>1.366</v>
       </c>
       <c r="T13" t="n">
-        <v>1.7764</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6753</v>
+        <v>0.5538999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>4.4401</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.0153</v>
+        <v>3.6225</v>
       </c>
       <c r="E14" t="n">
-        <v>4.7801</v>
+        <v>5.1016</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.7649</v>
+        <v>-1.4791</v>
       </c>
       <c r="G14" t="n">
         <v>1.72</v>
@@ -1546,13 +1546,13 @@
         <v>0.6244</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1429</v>
+        <v>0.4643</v>
       </c>
       <c r="T14" t="n">
-        <v>0.503</v>
+        <v>0.8244</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.6458</v>
+        <v>-0.3601</v>
       </c>
       <c r="V14" t="n">
         <v>0.8137</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P. ORENGA IMAZ</t>
+          <t>E. VAN DER HEIJDEN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.6271</v>
+        <v>1.8036</v>
       </c>
       <c r="E15" t="n">
-        <v>1.6497</v>
+        <v>0.8637</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.0227</v>
+        <v>0.9398</v>
       </c>
       <c r="G15" t="n">
-        <v>2.2203</v>
+        <v>0.3456</v>
       </c>
       <c r="H15" t="n">
-        <v>0.4413</v>
+        <v>-0.341</v>
       </c>
       <c r="I15" t="n">
-        <v>1.779</v>
+        <v>0.6866</v>
       </c>
       <c r="J15" t="n">
-        <v>0.7305</v>
+        <v>0.1501</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0251</v>
+        <v>-0.459</v>
       </c>
       <c r="L15" t="n">
-        <v>0.7054</v>
+        <v>0.609</v>
       </c>
       <c r="M15" t="n">
-        <v>1.4898</v>
+        <v>0.1956</v>
       </c>
       <c r="N15" t="n">
-        <v>0.4162</v>
+        <v>0.118</v>
       </c>
       <c r="O15" t="n">
-        <v>1.0736</v>
+        <v>0.0776</v>
       </c>
       <c r="P15" t="n">
-        <v>1.0406</v>
+        <v>-0.6244</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-2.2893</v>
       </c>
       <c r="R15" t="n">
-        <v>1.0406</v>
+        <v>1.6649</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1174</v>
+        <v>1.265</v>
       </c>
       <c r="T15" t="n">
-        <v>0.9192</v>
+        <v>1.6055</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.8018</v>
+        <v>-0.3405</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.7513</v>
+        <v>0.8173</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.3975</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.7513</v>
+        <v>-0.5802</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. HAYMAN</t>
+          <t>P. ORENGA IMAZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.1118</v>
+        <v>1.6603</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3908</v>
+        <v>1.2211</v>
       </c>
       <c r="F16" t="n">
-        <v>0.721</v>
+        <v>0.4392</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4158</v>
+        <v>2.2203</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9506</v>
+        <v>0.4413</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5348000000000001</v>
+        <v>1.779</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.0655</v>
+        <v>0.7305</v>
       </c>
       <c r="K16" t="n">
-        <v>0.8326</v>
+        <v>0.0251</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.8981</v>
+        <v>0.7054</v>
       </c>
       <c r="M16" t="n">
-        <v>0.4813</v>
+        <v>1.4898</v>
       </c>
       <c r="N16" t="n">
-        <v>0.118</v>
+        <v>0.4162</v>
       </c>
       <c r="O16" t="n">
-        <v>0.3633</v>
+        <v>1.0736</v>
       </c>
       <c r="P16" t="n">
-        <v>0.6244</v>
+        <v>1.0406</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.2487</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.8731</v>
+        <v>1.0406</v>
       </c>
       <c r="S16" t="n">
-        <v>0.8853</v>
+        <v>0.1507</v>
       </c>
       <c r="T16" t="n">
-        <v>1.475</v>
+        <v>0.4906</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5897</v>
+        <v>-0.3398</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.8137</v>
+        <v>-1.7513</v>
       </c>
       <c r="W16" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.0437</v>
+        <v>-1.7513</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>E. VAN DER HEIJDEN</t>
+          <t>D. HAYMAN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.0011</v>
+        <v>1.5047</v>
       </c>
       <c r="E17" t="n">
-        <v>0.4351</v>
+        <v>0.4979</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5659999999999999</v>
+        <v>1.0068</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3456</v>
+        <v>0.4158</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.341</v>
+        <v>0.9506</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6866</v>
+        <v>-0.5348000000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>0.1501</v>
+        <v>-0.0655</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.459</v>
+        <v>0.8326</v>
       </c>
       <c r="L17" t="n">
-        <v>0.609</v>
+        <v>-0.8981</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1956</v>
+        <v>0.4813</v>
       </c>
       <c r="N17" t="n">
         <v>0.118</v>
       </c>
       <c r="O17" t="n">
-        <v>0.0776</v>
+        <v>0.3633</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.6244</v>
+        <v>0.6244</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.2893</v>
+        <v>-1.2487</v>
       </c>
       <c r="R17" t="n">
-        <v>1.6649</v>
+        <v>1.8731</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4626</v>
+        <v>1.2782</v>
       </c>
       <c r="T17" t="n">
-        <v>1.1769</v>
+        <v>1.5822</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.7143</v>
+        <v>-0.3039</v>
       </c>
       <c r="V17" t="n">
-        <v>0.8173</v>
+        <v>-0.8137</v>
       </c>
       <c r="W17" t="n">
-        <v>1.3975</v>
+        <v>0.23</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.5802</v>
+        <v>-1.0437</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.8138</v>
+        <v>0.7579</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.7551</v>
+        <v>-0.4693</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9414</v>
+        <v>1.2271</v>
       </c>
       <c r="G18" t="n">
         <v>0.0238</v>
@@ -1858,13 +1858,13 @@
         <v>1.8731</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.5716</v>
+        <v>-0</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.0191</v>
+        <v>0.2668</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5525</v>
+        <v>-0.2668</v>
       </c>
       <c r="V18" t="n">
         <v>0.1097</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.632</v>
+        <v>-1.5731</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.2908</v>
+        <v>0.5665</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.3412</v>
+        <v>-2.1396</v>
       </c>
       <c r="G19" t="n">
         <v>-1.3145</v>
@@ -1936,13 +1936,13 @@
         <v>0.8325</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.9891</v>
+        <v>0.0698</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6805</v>
+        <v>0.1767</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3085</v>
+        <v>-0.107</v>
       </c>
       <c r="V19" t="n">
         <v>-0.1203</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.9231</v>
+        <v>-4.2152</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.0976</v>
+        <v>-2.4191</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.8255</v>
+        <v>-1.7961</v>
       </c>
       <c r="G20" t="n">
         <v>-4.0896</v>
@@ -2014,13 +2014,13 @@
         <v>0.4162</v>
       </c>
       <c r="S20" t="n">
-        <v>1.265</v>
+        <v>0.9729</v>
       </c>
       <c r="T20" t="n">
-        <v>1.2049</v>
+        <v>0.8835</v>
       </c>
       <c r="U20" t="n">
-        <v>0.06</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="V20" t="n">
         <v>-0.4741</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.1618</v>
+        <v>-5.6325</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.8898</v>
+        <v>-4.5328</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.2719</v>
+        <v>-1.0997</v>
       </c>
       <c r="G21" t="n">
         <v>-4.4646</v>
@@ -2092,13 +2092,13 @@
         <v>1.0406</v>
       </c>
       <c r="S21" t="n">
-        <v>1.4855</v>
+        <v>1.0148</v>
       </c>
       <c r="T21" t="n">
-        <v>1.646</v>
+        <v>1.003</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1605</v>
+        <v>0.0118</v>
       </c>
       <c r="V21" t="n">
         <v>-0.9340000000000001</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.4394</v>
+        <v>-6.914</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.2412</v>
+        <v>-4.8842</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.1981</v>
+        <v>-2.0298</v>
       </c>
       <c r="G22" t="n">
         <v>-2.5816</v>
@@ -2170,13 +2170,13 @@
         <v>0.6244</v>
       </c>
       <c r="S22" t="n">
-        <v>0.9747</v>
+        <v>0.5001</v>
       </c>
       <c r="T22" t="n">
-        <v>1.3354</v>
+        <v>0.6925</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3607</v>
+        <v>-0.1924</v>
       </c>
       <c r="V22" t="n">
         <v>-2.3351</v>
@@ -2203,31 +2203,31 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.063999999999998</v>
+        <v>1.079199999999998</v>
       </c>
       <c r="E23" t="n">
-        <v>4.282999999999997</v>
+        <v>4.2828</v>
       </c>
       <c r="F23" t="n">
-        <v>-5.346900000000001</v>
+        <v>-3.2038</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.6334</v>
+        <v>-2.633399999999999</v>
       </c>
       <c r="H23" t="n">
         <v>-7.6339</v>
       </c>
       <c r="I23" t="n">
-        <v>5.000699999999999</v>
+        <v>5.0007</v>
       </c>
       <c r="J23" t="n">
-        <v>2.022999999999998</v>
+        <v>2.023</v>
       </c>
       <c r="K23" t="n">
         <v>-3.6511</v>
       </c>
       <c r="L23" t="n">
-        <v>5.674099999999999</v>
+        <v>5.6741</v>
       </c>
       <c r="M23" t="n">
         <v>-4.6563</v>
@@ -2236,7 +2236,7 @@
         <v>-3.982799999999999</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.6736</v>
+        <v>-0.6735999999999995</v>
       </c>
       <c r="P23" t="n">
         <v>-3.1217</v>
@@ -2248,19 +2248,19 @@
         <v>11.4466</v>
       </c>
       <c r="S23" t="n">
-        <v>4.9386</v>
+        <v>7.0818</v>
       </c>
       <c r="T23" t="n">
-        <v>8.337199999999999</v>
+        <v>8.337200000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>-3.3985</v>
+        <v>-1.2554</v>
       </c>
       <c r="V23" t="n">
         <v>-0.2477000000000005</v>
       </c>
       <c r="W23" t="n">
-        <v>8.491200000000001</v>
+        <v>8.491199999999999</v>
       </c>
       <c r="X23" t="n">
         <v>-8.738900000000001</v>
